--- a/mutsu_water_rate/20_市長説明ライン/10_是正基準反映_2パターン_20261020/B_是正基準/03_改定率別純利益_B_是正基準.xlsx
+++ b/mutsu_water_rate/20_市長説明ライン/10_是正基準反映_2パターン_20261020/B_是正基準/03_改定率別純利益_B_是正基準.xlsx
@@ -330,7 +330,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="ja-JP"/>
         </a:p>
@@ -798,7 +798,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -860,7 +860,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -898,7 +898,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="ja-JP"/>
         </a:p>
@@ -1784,7 +1784,7 @@
         <v>0.073</v>
       </c>
       <c r="D3" s="30" t="n">
-        <v>1.077</v>
+        <v>1.023</v>
       </c>
       <c r="E3" s="30" t="n">
         <v>0.956</v>
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="I3" s="31" t="n">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="J3" s="31" t="n">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="K3" s="31" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="L3" s="31" t="n">
-        <v>71</v>
+        <v>-12</v>
       </c>
       <c r="M3" s="31" t="n">
-        <v>56</v>
+        <v>-26</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>37</v>
+        <v>-45</v>
       </c>
       <c r="P3" s="23" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>0.215</v>
       </c>
       <c r="D4" s="30" t="n">
-        <v>1.286</v>
+        <v>1.128</v>
       </c>
       <c r="E4" s="30" t="n">
         <v>1.083</v>
@@ -1871,22 +1871,22 @@
         </is>
       </c>
       <c r="I4" s="31" t="n">
-        <v>459</v>
+        <v>205</v>
       </c>
       <c r="J4" s="31" t="n">
-        <v>443</v>
+        <v>192</v>
       </c>
       <c r="K4" s="31" t="n">
-        <v>419</v>
+        <v>170</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>397</v>
+        <v>150</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>379</v>
+        <v>135</v>
       </c>
       <c r="N4" s="31" t="n">
-        <v>356</v>
+        <v>115</v>
       </c>
       <c r="P4" s="33" t="n"/>
       <c r="Q4" s="33" t="n"/>
@@ -1907,7 +1907,7 @@
         <v>0.357</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>1.495</v>
+        <v>1.232</v>
       </c>
       <c r="E5" s="30" t="n">
         <v>1.209</v>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="I5" s="31" t="n">
-        <v>795</v>
+        <v>373</v>
       </c>
       <c r="J5" s="31" t="n">
-        <v>776</v>
+        <v>358</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>748</v>
+        <v>335</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>722</v>
+        <v>313</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>701</v>
+        <v>296</v>
       </c>
       <c r="N5" s="31" t="n">
-        <v>676</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
@@ -1947,7 +1947,7 @@
         <v>0.498</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>1.703</v>
+        <v>1.337</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>1.336</v>
@@ -1961,22 +1961,22 @@
         </is>
       </c>
       <c r="I6" s="34" t="n">
-        <v>1130</v>
+        <v>541</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>1108</v>
+        <v>524</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>1077</v>
+        <v>499</v>
       </c>
       <c r="L6" s="34" t="n">
-        <v>1048</v>
+        <v>476</v>
       </c>
       <c r="M6" s="34" t="n">
-        <v>1024</v>
+        <v>457</v>
       </c>
       <c r="N6" s="34" t="n">
-        <v>995</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
